--- a/2026/BELTRAN 34/Septiembre/Septiembre BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Septiembre/Septiembre BELTRAN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194BC290-6F03-4F6D-A6B9-40857D8D3308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BA7C1E-166B-449F-A16E-C581B61B006E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$94</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="133">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>GASTOS EXTRAORDINARIOS UNIDADES FUNCIONALES:</t>
-  </si>
-  <si>
-    <t>PREVISION EXTRAORDINARIA</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL EXTRAORDINARIOS </t>
@@ -393,49 +390,49 @@
     <t>$157.200 transfririo el 1° C. + Cochera C</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
     <t>Subido en Juli0 a $91.000</t>
   </si>
   <si>
-    <t>VTO 17/09</t>
-  </si>
-  <si>
-    <t>Transf 05/08</t>
-  </si>
-  <si>
-    <t>Transf 12/08</t>
-  </si>
-  <si>
-    <t>Celestino Soledad - Servicio de limpieza - Mes de Julio (tomo vacaciones) y Agosto</t>
-  </si>
-  <si>
-    <t>Transf 28/08</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>Julio</t>
-  </si>
-  <si>
     <t>Federacion patronal - Seguro integral de consorcio</t>
   </si>
   <si>
-    <t>Debito 28/08</t>
-  </si>
-  <si>
-    <t>Honorarios administracion -  JULIO Y AGOSTO</t>
-  </si>
-  <si>
-    <t>Transf 30/08</t>
-  </si>
-  <si>
     <t>Seguro - Sra. Soledad - La Holando - Poliza nro. 690173-2</t>
   </si>
   <si>
     <t>Hay una diferencia de caja correspondiente a un gasto de AYSA a solucionar en S3ptiembr3</t>
+  </si>
+  <si>
+    <t>VTO 16/10</t>
+  </si>
+  <si>
+    <t>Transf 07/09</t>
+  </si>
+  <si>
+    <t>Gasto particular: Desglose deuda para presentar en juzgado</t>
+  </si>
+  <si>
+    <t>Kromacolor pinturerias - Compra de recuplast, venda y rodillos para trabajo en terraza</t>
+  </si>
+  <si>
+    <t>Transf 16/09</t>
+  </si>
+  <si>
+    <t>Adelanto Mano de obra - Sr. Facundo Heredia</t>
+  </si>
+  <si>
+    <t>Transf  23/09</t>
+  </si>
+  <si>
+    <t>Debito 28/09</t>
+  </si>
+  <si>
+    <t>Honorarios administracion -  Se adeuda Septiembre</t>
+  </si>
+  <si>
+    <t>Celestino Soledad - Servicio de limpieza - No se abona por falta de fondos</t>
+  </si>
+  <si>
+    <t>PREVISION EXTRAORDINARIA - Monto de inicio de demanda $144.411</t>
   </si>
 </sst>
 </file>
@@ -451,7 +448,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -736,6 +733,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -1474,7 +1478,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1673,6 +1677,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1682,6 +1696,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1709,6 +1726,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1766,18 +1789,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="42" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -2207,7 +2219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2222,7 +2234,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="74" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="70"/>
       <c r="C1" s="2"/>
@@ -2230,7 +2242,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="71"/>
       <c r="C2" s="71"/>
@@ -2238,48 +2250,48 @@
     </row>
     <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
       <c r="A3" s="71" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" s="71"/>
       <c r="C3" s="71"/>
       <c r="D3" s="71"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A4" s="148" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="148"/>
+      <c r="A4" s="154" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="154"/>
       <c r="C4" s="72"/>
       <c r="D4" s="72"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
+      <c r="A5" s="154"/>
+      <c r="B5" s="154"/>
       <c r="C5" s="72"/>
       <c r="D5" s="72"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="148"/>
-      <c r="B6" s="148"/>
+      <c r="A6" s="154"/>
+      <c r="B6" s="154"/>
       <c r="C6" s="72"/>
       <c r="D6" s="72"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="148"/>
-      <c r="B7" s="148"/>
+      <c r="A7" s="154"/>
+      <c r="B7" s="154"/>
       <c r="C7" s="72"/>
       <c r="D7" s="72"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="155" t="s">
-        <v>121</v>
+      <c r="B9" s="162" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="155"/>
+      <c r="B10" s="162"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="155"/>
+      <c r="B11" s="162"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="62"/>
@@ -2294,30 +2306,30 @@
       <c r="D13" s="62"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="179" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="179"/>
-      <c r="C14" s="179"/>
-      <c r="D14" s="179"/>
+      <c r="A14" s="157" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="157"/>
+      <c r="C14" s="157"/>
+      <c r="D14" s="157"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="179"/>
-      <c r="B15" s="179"/>
-      <c r="C15" s="179"/>
-      <c r="D15" s="179"/>
+      <c r="A15" s="157"/>
+      <c r="B15" s="157"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="157"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="179"/>
-      <c r="B16" s="179"/>
-      <c r="C16" s="179"/>
-      <c r="D16" s="179"/>
+      <c r="A16" s="157"/>
+      <c r="B16" s="157"/>
+      <c r="C16" s="157"/>
+      <c r="D16" s="157"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="179"/>
-      <c r="B17" s="179"/>
-      <c r="C17" s="179"/>
-      <c r="D17" s="179"/>
+      <c r="A17" s="157"/>
+      <c r="B17" s="157"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="157"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="A18" s="62"/>
@@ -2326,7 +2338,7 @@
       <c r="D18" s="62"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
-      <c r="A19" s="180"/>
+      <c r="A19" s="149"/>
       <c r="B19" s="62"/>
       <c r="C19" s="62"/>
       <c r="D19" s="62"/>
@@ -2347,7 +2359,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -2355,29 +2367,29 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A23" s="156" t="s">
-        <v>124</v>
-      </c>
-      <c r="B23" s="157"/>
-      <c r="C23" s="181">
-        <v>450000</v>
+      <c r="A23" s="163" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="164"/>
+      <c r="C23" s="167">
+        <v>0</v>
       </c>
       <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A24" s="158"/>
-      <c r="B24" s="159"/>
-      <c r="C24" s="182"/>
+      <c r="A24" s="165"/>
+      <c r="B24" s="166"/>
+      <c r="C24" s="168"/>
       <c r="D24" s="48"/>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="111" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="111"/>
       <c r="C25" s="142">
         <f>SUM(C23:C24)</f>
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="D25" s="49"/>
     </row>
@@ -2407,7 +2419,7 @@
     </row>
     <row r="30" spans="1:7" hidden="1">
       <c r="A30" s="111" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" s="112"/>
       <c r="C30" s="22">
@@ -2424,7 +2436,7 @@
       <c r="C31" s="5"/>
       <c r="D31" s="50">
         <f>C25+C30</f>
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -2444,14 +2456,11 @@
       </c>
       <c r="B33" s="113"/>
       <c r="C33" s="84">
-        <f>91000*2</f>
-        <v>182000</v>
-      </c>
-      <c r="D33" s="82" t="s">
-        <v>131</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D33" s="82"/>
       <c r="F33" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G33" s="4"/>
     </row>
@@ -2463,23 +2472,23 @@
       <c r="C34" s="143"/>
       <c r="D34" s="50">
         <f>SUM(C33:C33)</f>
-        <v>182000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="16.5" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="11"/>
       <c r="D35" s="27"/>
     </row>
     <row r="36" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A36" s="149" t="s">
-        <v>128</v>
-      </c>
-      <c r="B36" s="150"/>
-      <c r="C36" s="183">
+      <c r="A36" s="155" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="156"/>
+      <c r="C36" s="152">
         <v>89533</v>
       </c>
       <c r="D36" s="81" t="s">
@@ -2488,10 +2497,10 @@
     </row>
     <row r="37" spans="1:7" ht="22.5" customHeight="1">
       <c r="A37" s="146" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B37" s="147"/>
-      <c r="C37" s="184">
+      <c r="C37" s="153">
         <v>5587.48</v>
       </c>
       <c r="D37" s="81" t="s">
@@ -2519,10 +2528,10 @@
     </row>
     <row r="40" spans="1:7" hidden="1">
       <c r="A40" s="48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C40" s="86"/>
       <c r="D40" s="81"/>
@@ -2530,30 +2539,30 @@
     </row>
     <row r="41" spans="1:7" hidden="1">
       <c r="A41" s="48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C41" s="87"/>
       <c r="D41" s="81"/>
     </row>
     <row r="42" spans="1:7" hidden="1">
       <c r="A42" s="48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C42" s="87"/>
       <c r="D42" s="81"/>
     </row>
     <row r="43" spans="1:7" hidden="1">
       <c r="A43" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C43" s="87"/>
       <c r="D43" s="80"/>
@@ -2579,29 +2588,29 @@
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1">
       <c r="A46" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B46" s="48"/>
-      <c r="C46" s="87">
-        <v>86429.79</v>
+      <c r="C46" s="150">
+        <v>66626.53</v>
       </c>
       <c r="D46" s="79" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1">
       <c r="A47" s="48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B47" s="48"/>
-      <c r="C47" s="87">
-        <v>392672.62</v>
+      <c r="C47" s="150">
+        <v>502776.73</v>
       </c>
       <c r="D47" s="79" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" thickBot="1">
@@ -2612,7 +2621,7 @@
       <c r="C48" s="13"/>
       <c r="D48" s="52">
         <f>SUM(C46:C47)</f>
-        <v>479102.41</v>
+        <v>569403.26</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
@@ -2624,43 +2633,39 @@
       <c r="D49" s="55"/>
     </row>
     <row r="50" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A50" s="149" t="s">
-        <v>110</v>
-      </c>
-      <c r="B50" s="150"/>
-      <c r="C50" s="87">
+      <c r="A50" s="155" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="156"/>
+      <c r="C50" s="150">
         <v>126000</v>
       </c>
-      <c r="D50" s="77" t="s">
+      <c r="D50" s="79" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="19.899999999999999" customHeight="1">
       <c r="A51" s="146" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="148"/>
+      <c r="C51" s="150">
+        <v>300000</v>
+      </c>
+      <c r="D51" s="77" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="41.25" customHeight="1">
+      <c r="A52" s="155" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="156"/>
+      <c r="C52" s="150">
+        <v>580730.54</v>
+      </c>
+      <c r="D52" s="77" t="s">
         <v>126</v>
-      </c>
-      <c r="C51" s="87">
-        <v>29400</v>
-      </c>
-      <c r="D51" s="77" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A52" s="146" t="s">
-        <v>119</v>
-      </c>
-      <c r="B52" s="147" t="s">
-        <v>127</v>
-      </c>
-      <c r="C52" s="87">
-        <v>37600</v>
-      </c>
-      <c r="D52" s="77" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
@@ -2671,7 +2676,7 @@
       <c r="C53" s="8"/>
       <c r="D53" s="57">
         <f>SUM(C50:C52)</f>
-        <v>193000</v>
+        <v>1006730.54</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
@@ -2684,21 +2689,21 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B55" s="48"/>
-      <c r="C55" s="87">
+      <c r="C55" s="150">
         <v>69000</v>
       </c>
       <c r="D55" s="58"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B56" s="48"/>
-      <c r="C56" s="87">
-        <v>40355.57</v>
+      <c r="C56" s="150">
+        <v>39863.769999999997</v>
       </c>
       <c r="D56" s="56"/>
     </row>
@@ -2710,7 +2715,7 @@
       <c r="C57" s="59"/>
       <c r="D57" s="52">
         <f>SUM(C55:C56)</f>
-        <v>109355.57</v>
+        <v>108863.76999999999</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
@@ -2720,11 +2725,11 @@
       <c r="D58" s="60"/>
     </row>
     <row r="59" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A59" s="152" t="s">
-        <v>114</v>
-      </c>
-      <c r="B59" s="153"/>
-      <c r="C59" s="154"/>
+      <c r="A59" s="159" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" s="160"/>
+      <c r="C59" s="161"/>
       <c r="D59" s="61">
         <v>0</v>
       </c>
@@ -2744,7 +2749,7 @@
       <c r="C61" s="64"/>
       <c r="D61" s="65">
         <f>(SUM(D26:D59))</f>
-        <v>1508578.46</v>
+        <v>1780118.05</v>
       </c>
       <c r="E61" s="18"/>
       <c r="F61" s="18"/>
@@ -2799,12 +2804,12 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="128" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="B69" s="128"/>
       <c r="C69" s="129"/>
       <c r="D69" s="83">
-        <v>0</v>
+        <v>144411</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" thickBot="1">
@@ -2814,13 +2819,13 @@
     </row>
     <row r="71" spans="1:4" ht="15.75" thickBot="1">
       <c r="A71" s="118" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B71" s="119"/>
       <c r="C71" s="64"/>
       <c r="D71" s="28">
         <f>D66+D69</f>
-        <v>0</v>
+        <v>144411</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" thickBot="1">
@@ -2834,7 +2839,7 @@
       </c>
       <c r="B73" s="131">
         <f>D61</f>
-        <v>1508578.46</v>
+        <v>1780118.05</v>
       </c>
       <c r="C73" s="132"/>
     </row>
@@ -2844,13 +2849,13 @@
       </c>
       <c r="B74" s="131">
         <f>D61-D59</f>
-        <v>1508578.46</v>
+        <v>1780118.05</v>
       </c>
       <c r="C74" s="62"/>
     </row>
     <row r="75" spans="1:4" ht="15.75" thickBot="1">
       <c r="A75" s="130" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B75" s="131">
         <f>D71-D69</f>
@@ -2860,11 +2865,11 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" thickBot="1">
       <c r="A76" s="130" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B76" s="131">
         <f>D71</f>
-        <v>0</v>
+        <v>144411</v>
       </c>
       <c r="C76" s="62"/>
     </row>
@@ -2873,7 +2878,7 @@
       <c r="B77" s="62"/>
       <c r="C77" s="62"/>
       <c r="D77" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2888,7 +2893,7 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" thickBot="1">
       <c r="A80" s="133" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B80" s="134"/>
       <c r="C80" s="62"/>
@@ -2898,109 +2903,119 @@
         <v>28</v>
       </c>
       <c r="B81" s="135">
-        <v>1118920.2499999998</v>
+        <v>1003717.69</v>
       </c>
       <c r="C81" s="62"/>
     </row>
     <row r="82" spans="1:12" ht="14.25" customHeight="1">
       <c r="A82" s="136" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B82" s="56">
         <f>PRORRATEO!H24</f>
-        <v>1393375.9</v>
+        <v>1248334.8199999998</v>
       </c>
       <c r="C82" s="62"/>
     </row>
     <row r="83" spans="1:12" ht="14.25" customHeight="1">
       <c r="A83" s="136" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B83" s="56">
-        <f>B92</f>
+        <f>B93</f>
         <v>0</v>
       </c>
       <c r="C83" s="62"/>
       <c r="F83" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" s="138" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="39.75" customHeight="1">
+      <c r="A84" s="151" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="144">
+        <v>-50000</v>
+      </c>
+      <c r="C84" s="62"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="138" t="s">
+        <v>37</v>
+      </c>
+      <c r="B85" s="144">
+        <f>-B74</f>
+        <v>-1780118.05</v>
+      </c>
+      <c r="C85" s="62"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="B84" s="144">
-        <f>-B74</f>
-        <v>-1508578.46</v>
-      </c>
-      <c r="C84" s="62"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" s="137" t="s">
-        <v>39</v>
-      </c>
-      <c r="B85" s="56">
+      <c r="B86" s="56">
         <f>-(B75)</f>
         <v>0</v>
       </c>
-      <c r="C85" s="62"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" s="6" t="s">
+      <c r="C86" s="62"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B86" s="98">
-        <f>SUM(B81:B85)</f>
-        <v>1003717.6899999995</v>
-      </c>
-      <c r="C86" s="123"/>
-    </row>
-    <row r="87" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B87" s="16"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="123"/>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="A88" s="151" t="s">
-        <v>46</v>
-      </c>
-      <c r="B88" s="151"/>
-    </row>
-    <row r="89" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A89" s="151"/>
-      <c r="B89" s="151"/>
-    </row>
-    <row r="90" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A90" s="68"/>
-      <c r="B90" s="12"/>
+      <c r="B87" s="98">
+        <f>SUM(B81:B86)</f>
+        <v>421934.45999999973</v>
+      </c>
+      <c r="C87" s="123"/>
+    </row>
+    <row r="88" spans="1:12" ht="34.5" customHeight="1">
+      <c r="B88" s="16"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="123"/>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" s="158" t="s">
+        <v>45</v>
+      </c>
+      <c r="B89" s="158"/>
+    </row>
+    <row r="90" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A90" s="158"/>
+      <c r="B90" s="158"/>
     </row>
     <row r="91" spans="1:12" ht="32.25" customHeight="1">
       <c r="A91" s="68"/>
       <c r="B91" s="12"/>
     </row>
-    <row r="92" spans="1:12">
-      <c r="A92" s="19" t="s">
+    <row r="92" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A92" s="68"/>
+      <c r="B92" s="12"/>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B92" s="69">
-        <f>SUM(B90:B91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12">
-      <c r="L93" s="3"/>
+      <c r="B93" s="69">
+        <f>SUM(B91:B92)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="L94" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A88:B89"/>
+    <mergeCell ref="A89:B90"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A23:B24"/>
     <mergeCell ref="C23:C24"/>
+    <mergeCell ref="A52:B52"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3037,22 +3052,22 @@
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="99"/>
-      <c r="B1" s="160" t="str">
+      <c r="B1" s="169" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
       <c r="L1" s="100"/>
       <c r="M1" s="100"/>
       <c r="N1" s="100"/>
@@ -3061,23 +3076,23 @@
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
       <c r="A2" s="102"/>
-      <c r="B2" s="161"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="170"/>
       <c r="L2" s="103"/>
       <c r="M2" s="103" t="s">
         <v>4</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="110">
-        <v>1508578.46</v>
+        <v>1780118.05</v>
       </c>
       <c r="P2" s="104"/>
       <c r="Q2" s="4"/>
@@ -3087,118 +3102,118 @@
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
       <c r="A3" s="105"/>
-      <c r="B3" s="162"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="162"/>
-      <c r="K3" s="162"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
       <c r="L3" s="106"/>
       <c r="M3" s="106" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N3" s="107"/>
       <c r="O3" s="140">
-        <v>0</v>
+        <v>144411</v>
       </c>
       <c r="P3" s="108"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="173" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="174"/>
-      <c r="E4" s="174"/>
-      <c r="F4" s="174"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="174"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="174"/>
-      <c r="K4" s="174"/>
-      <c r="L4" s="174"/>
-      <c r="M4" s="174"/>
-      <c r="N4" s="174"/>
-      <c r="O4" s="174"/>
-      <c r="P4" s="175"/>
+      <c r="B4" s="182" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
+      <c r="H4" s="183"/>
+      <c r="I4" s="183"/>
+      <c r="J4" s="183"/>
+      <c r="K4" s="183"/>
+      <c r="L4" s="183"/>
+      <c r="M4" s="183"/>
+      <c r="N4" s="183"/>
+      <c r="O4" s="183"/>
+      <c r="P4" s="184"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="185" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="178" t="s">
+      <c r="B5" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="165" t="s">
+      <c r="C5" s="174" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="165" t="s">
+      <c r="D5" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="165" t="s">
+      <c r="E5" s="174" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="174" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="174" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="174" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="174" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="165" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="165" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="165" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="165" t="s">
+      <c r="J5" s="178" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="169" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="167" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="167" t="s">
+      <c r="K5" s="176" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="167" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" s="171" t="s">
-        <v>51</v>
+      <c r="M5" s="176" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="180" t="s">
+        <v>50</v>
       </c>
       <c r="O5" s="88" t="s">
-        <v>50</v>
-      </c>
-      <c r="P5" s="163" t="s">
         <v>49</v>
+      </c>
+      <c r="P5" s="172" t="s">
+        <v>48</v>
       </c>
       <c r="S5" s="18"/>
       <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="177"/>
-      <c r="B6" s="178"/>
-      <c r="C6" s="165"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="166"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="165"/>
-      <c r="H6" s="165"/>
-      <c r="I6" s="166"/>
-      <c r="J6" s="170"/>
-      <c r="K6" s="168"/>
-      <c r="L6" s="167"/>
-      <c r="M6" s="168"/>
-      <c r="N6" s="172"/>
+      <c r="A6" s="186"/>
+      <c r="B6" s="187"/>
+      <c r="C6" s="174"/>
+      <c r="D6" s="174"/>
+      <c r="E6" s="175"/>
+      <c r="F6" s="174"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="174"/>
+      <c r="I6" s="175"/>
+      <c r="J6" s="179"/>
+      <c r="K6" s="177"/>
+      <c r="L6" s="176"/>
+      <c r="M6" s="177"/>
+      <c r="N6" s="181"/>
       <c r="O6" s="23" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 17/09</v>
-      </c>
-      <c r="P6" s="163"/>
+        <v>VTO 16/10</v>
+      </c>
+      <c r="P6" s="172"/>
       <c r="S6" s="16">
         <v>65160</v>
       </c>
@@ -3218,46 +3233,46 @@
         <v>1</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="29">
         <v>10.86</v>
       </c>
       <c r="G7" s="30">
-        <v>5442105.0099999998</v>
+        <v>5844200.0099999998</v>
       </c>
       <c r="H7" s="31"/>
       <c r="I7" s="32"/>
       <c r="J7" s="33">
         <f>G7-H7</f>
-        <v>5442105.0099999998</v>
+        <v>5844200.0099999998</v>
       </c>
       <c r="K7" s="33">
         <f>IF(J7&gt;0,J7*3%,0)</f>
-        <v>163263.15029999998</v>
+        <v>175326.00029999999</v>
       </c>
       <c r="L7" s="34">
         <f>O$3*F7%</f>
-        <v>0</v>
+        <v>15683.034599999999</v>
       </c>
       <c r="M7" s="34">
         <f>O$2*F7%</f>
-        <v>163831.62075599999</v>
+        <v>193320.82022999998</v>
       </c>
       <c r="N7" s="35">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="O7" s="36">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>5844200.0099999998</v>
+        <v>6278530.0099999998</v>
       </c>
       <c r="P7" s="37">
         <f t="shared" ref="P7:P23" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>6019526.0099999998</v>
+        <v>6466886.0099999998</v>
       </c>
       <c r="Q7" s="18">
         <v>0.01</v>
@@ -3281,49 +3296,49 @@
         <v>2</v>
       </c>
       <c r="C8" s="78" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" s="78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" s="90"/>
       <c r="F8" s="29">
         <v>11.16</v>
       </c>
       <c r="G8" s="30">
-        <v>189302.02</v>
-      </c>
-      <c r="H8" s="31">
-        <f>198971-H18</f>
-        <v>189301.88</v>
+        <v>173409.02</v>
+      </c>
+      <c r="H8" s="188">
+        <f>182266.14-H18</f>
+        <v>173409.02000000002</v>
       </c>
       <c r="I8" s="32"/>
       <c r="J8" s="33">
         <f t="shared" ref="J8:J22" si="2">G8-H8</f>
-        <v>0.13999999998486601</v>
+        <v>0</v>
       </c>
       <c r="K8" s="33">
         <f t="shared" ref="K8:K22" si="3">IF(J8&gt;0,J8*3%,0)</f>
-        <v>4.1999999995459801E-3</v>
+        <v>0</v>
       </c>
       <c r="L8" s="34">
         <f t="shared" ref="L8:L23" si="4">O$3*F8%</f>
-        <v>0</v>
+        <v>16116.267600000001</v>
       </c>
       <c r="M8" s="34">
         <f t="shared" ref="M8:M23" si="5">O$2*F8%</f>
-        <v>168357.35613600002</v>
+        <v>198661.17438000001</v>
       </c>
       <c r="N8" s="35">
         <v>0</v>
       </c>
       <c r="O8" s="36">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>168358.02</v>
+        <v>214777.02</v>
       </c>
       <c r="P8" s="37">
         <f t="shared" si="0"/>
-        <v>173409.02</v>
+        <v>221220.02</v>
       </c>
       <c r="Q8" s="18">
         <f>Q7+0.01</f>
@@ -3349,50 +3364,50 @@
         <v>4</v>
       </c>
       <c r="C9" s="78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D9" s="89" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" s="78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F9" s="91">
         <v>6.95</v>
       </c>
       <c r="G9" s="31">
-        <v>232394.03</v>
+        <v>226272.03</v>
       </c>
       <c r="H9" s="31">
-        <v>114505</v>
+        <v>0</v>
       </c>
       <c r="I9" s="32"/>
       <c r="J9" s="92">
         <f t="shared" si="2"/>
-        <v>117889.03</v>
+        <v>226272.03</v>
       </c>
       <c r="K9" s="33">
         <f t="shared" si="3"/>
-        <v>3536.6708999999996</v>
+        <v>6788.1608999999999</v>
       </c>
       <c r="L9" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10036.5645</v>
       </c>
       <c r="M9" s="93">
         <f t="shared" si="5"/>
-        <v>104846.20297000001</v>
+        <v>123718.20447500002</v>
       </c>
       <c r="N9" s="94">
         <v>0</v>
       </c>
       <c r="O9" s="95">
         <f t="shared" ref="O9:O23" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>226272.03</v>
+        <v>366815.03</v>
       </c>
       <c r="P9" s="96">
         <f t="shared" si="0"/>
-        <v>233060.03</v>
+        <v>377819.03</v>
       </c>
       <c r="Q9" s="18">
         <f t="shared" ref="Q9:Q22" si="7">Q8+0.01</f>
@@ -3417,51 +3432,51 @@
         <v>3</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D10" s="78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" s="78" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F10" s="29">
         <v>7.37</v>
       </c>
       <c r="G10" s="30">
-        <v>168311.04000000001</v>
-      </c>
-      <c r="H10" s="31">
-        <f>129937-H20</f>
-        <v>121372.86</v>
+        <v>159529.04</v>
+      </c>
+      <c r="H10" s="188">
+        <f>119027-H20</f>
+        <v>111181.86</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="33">
         <f t="shared" si="2"/>
-        <v>46938.180000000008</v>
+        <v>48347.180000000008</v>
       </c>
       <c r="K10" s="33">
         <f t="shared" si="3"/>
-        <v>1408.1454000000001</v>
+        <v>1450.4154000000001</v>
       </c>
       <c r="L10" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10643.090700000001</v>
       </c>
       <c r="M10" s="34">
         <f t="shared" si="5"/>
-        <v>111182.232502</v>
+        <v>131194.700285</v>
       </c>
       <c r="N10" s="35">
         <v>0</v>
       </c>
       <c r="O10" s="36">
         <f t="shared" si="6"/>
-        <v>159529.04</v>
+        <v>191635.04</v>
       </c>
       <c r="P10" s="37">
         <f t="shared" si="0"/>
-        <v>164315.04</v>
+        <v>197384.04</v>
       </c>
       <c r="Q10" s="18">
         <f t="shared" si="7"/>
@@ -3486,23 +3501,23 @@
         <v>5</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F11" s="29">
         <v>10.68</v>
       </c>
       <c r="G11" s="30">
-        <v>170607.05</v>
-      </c>
-      <c r="H11" s="31">
+        <v>161116.04999999999</v>
+      </c>
+      <c r="H11" s="188">
         <f>G11</f>
-        <v>170607.05</v>
+        <v>161116.04999999999</v>
       </c>
       <c r="I11" s="32"/>
       <c r="J11" s="33">
@@ -3515,22 +3530,22 @@
       </c>
       <c r="L11" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15423.094799999999</v>
       </c>
       <c r="M11" s="34">
         <f t="shared" si="5"/>
-        <v>161116.17952799998</v>
+        <v>190116.60773999998</v>
       </c>
       <c r="N11" s="35">
         <v>0</v>
       </c>
       <c r="O11" s="36">
         <f t="shared" si="6"/>
-        <v>161116.04999999999</v>
+        <v>205540.05</v>
       </c>
       <c r="P11" s="37">
         <f t="shared" si="0"/>
-        <v>165949.04999999999</v>
+        <v>211706.05</v>
       </c>
       <c r="Q11" s="18">
         <f t="shared" si="7"/>
@@ -3555,51 +3570,51 @@
         <v>7</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F12" s="29">
         <v>6.95</v>
       </c>
       <c r="G12" s="30">
-        <v>114456.06</v>
-      </c>
-      <c r="H12" s="31">
-        <f>G12</f>
-        <v>114456.06</v>
+        <v>104846.06</v>
+      </c>
+      <c r="H12" s="188">
+        <f>114048-H22</f>
+        <v>104845.84</v>
       </c>
       <c r="I12" s="32"/>
       <c r="J12" s="33">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.22000000000116415</v>
       </c>
       <c r="K12" s="33">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.6000000000349243E-3</v>
       </c>
       <c r="L12" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10036.5645</v>
       </c>
       <c r="M12" s="34">
         <f t="shared" si="5"/>
-        <v>104846.20297000001</v>
+        <v>123718.20447500002</v>
       </c>
       <c r="N12" s="122">
         <v>0</v>
       </c>
       <c r="O12" s="36">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>104846.06</v>
+        <v>133755.06</v>
       </c>
       <c r="P12" s="37">
         <f t="shared" si="0"/>
-        <v>107991.06</v>
+        <v>137768.06</v>
       </c>
       <c r="Q12" s="18">
         <f t="shared" si="7"/>
@@ -3624,23 +3639,23 @@
         <v>6</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" s="78" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F13" s="29">
         <v>6.89</v>
       </c>
       <c r="G13" s="30">
-        <v>113468.07</v>
-      </c>
-      <c r="H13" s="31">
+        <v>103941.07</v>
+      </c>
+      <c r="H13" s="188">
         <f>G13</f>
-        <v>113468.07</v>
+        <v>103941.07</v>
       </c>
       <c r="I13" s="32"/>
       <c r="J13" s="33">
@@ -3653,22 +3668,22 @@
       </c>
       <c r="L13" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9949.9179000000004</v>
       </c>
       <c r="M13" s="34">
         <f t="shared" si="5"/>
-        <v>103941.055894</v>
+        <v>122650.13364500001</v>
       </c>
       <c r="N13" s="35">
         <v>0</v>
       </c>
       <c r="O13" s="36">
         <f t="shared" si="6"/>
-        <v>103941.07</v>
+        <v>132600.07</v>
       </c>
       <c r="P13" s="37">
         <f t="shared" si="0"/>
-        <v>107059.07</v>
+        <v>136578.07</v>
       </c>
       <c r="Q13" s="18">
         <f t="shared" si="7"/>
@@ -3694,23 +3709,23 @@
         <v>8</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F14" s="29">
         <v>10.68</v>
       </c>
       <c r="G14" s="30">
-        <v>175883.08</v>
-      </c>
-      <c r="H14" s="31">
+        <v>161116.07999999999</v>
+      </c>
+      <c r="H14" s="188">
         <f>G14</f>
-        <v>175883.08</v>
+        <v>161116.07999999999</v>
       </c>
       <c r="I14" s="32"/>
       <c r="J14" s="33">
@@ -3723,22 +3738,22 @@
       </c>
       <c r="L14" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15423.094799999999</v>
       </c>
       <c r="M14" s="34">
         <f t="shared" si="5"/>
-        <v>161116.17952799998</v>
+        <v>190116.60773999998</v>
       </c>
       <c r="N14" s="35">
         <v>0</v>
       </c>
       <c r="O14" s="36">
         <f t="shared" si="6"/>
-        <v>161116.07999999999</v>
+        <v>205540.08</v>
       </c>
       <c r="P14" s="37">
         <f t="shared" si="0"/>
-        <v>165949.07999999999</v>
+        <v>211706.08</v>
       </c>
       <c r="Q14" s="18">
         <f t="shared" si="7"/>
@@ -3763,50 +3778,49 @@
         <v>10</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" s="78" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E15" s="90" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F15" s="91">
         <v>6.95</v>
       </c>
       <c r="G15" s="31">
-        <v>39268.089999999997</v>
-      </c>
-      <c r="H15" s="31">
-        <f>G15</f>
-        <v>39268.089999999997</v>
+        <v>104846.09</v>
+      </c>
+      <c r="H15" s="188">
+        <v>107991.09</v>
       </c>
       <c r="I15" s="32"/>
       <c r="J15" s="92">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3145</v>
       </c>
       <c r="K15" s="92">
         <v>0</v>
       </c>
       <c r="L15" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10036.5645</v>
       </c>
       <c r="M15" s="93">
         <f t="shared" si="5"/>
-        <v>104846.20297000001</v>
+        <v>123718.20447500002</v>
       </c>
       <c r="N15" s="94">
         <v>0</v>
       </c>
       <c r="O15" s="95">
         <f t="shared" si="6"/>
-        <v>104846.09</v>
+        <v>130610.09</v>
       </c>
       <c r="P15" s="96">
         <f t="shared" si="0"/>
-        <v>107991.09</v>
+        <v>134528.09</v>
       </c>
       <c r="Q15" s="18">
         <f t="shared" si="7"/>
@@ -3831,57 +3845,57 @@
         <v>9</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F16" s="29">
         <v>6.89</v>
       </c>
       <c r="G16" s="30">
-        <v>154767.1</v>
-      </c>
-      <c r="H16" s="31">
-        <v>113468</v>
+        <v>146479.1</v>
+      </c>
+      <c r="H16" s="188">
+        <v>103941</v>
       </c>
       <c r="I16" s="32"/>
       <c r="J16" s="33">
         <f t="shared" si="2"/>
-        <v>41299.100000000006</v>
+        <v>42538.100000000006</v>
       </c>
       <c r="K16" s="33">
         <f t="shared" si="3"/>
-        <v>1238.9730000000002</v>
+        <v>1276.143</v>
       </c>
       <c r="L16" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9949.9179000000004</v>
       </c>
       <c r="M16" s="34">
         <f t="shared" si="5"/>
-        <v>103941.055894</v>
+        <v>122650.13364500001</v>
       </c>
       <c r="N16" s="35">
         <v>0</v>
       </c>
       <c r="O16" s="36">
         <f t="shared" si="6"/>
-        <v>146479.1</v>
+        <v>176414.1</v>
       </c>
       <c r="P16" s="37">
         <f t="shared" si="0"/>
-        <v>150873.1</v>
+        <v>181706.1</v>
       </c>
       <c r="Q16" s="18">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="S16" s="16">
         <v>71280</v>
@@ -3902,21 +3916,21 @@
         <v>11</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" s="26"/>
       <c r="F17" s="29">
         <v>11.88</v>
       </c>
       <c r="G17" s="30">
-        <v>195646.11</v>
-      </c>
-      <c r="H17" s="31">
+        <v>179219.11</v>
+      </c>
+      <c r="H17" s="188">
         <f>G17</f>
-        <v>195646.11</v>
+        <v>179219.11</v>
       </c>
       <c r="I17" s="32"/>
       <c r="J17" s="33">
@@ -3929,29 +3943,29 @@
       </c>
       <c r="L17" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17156.0268</v>
       </c>
       <c r="M17" s="34">
         <f t="shared" si="5"/>
-        <v>179219.121048</v>
+        <v>211478.02434</v>
       </c>
       <c r="N17" s="35">
         <v>0</v>
       </c>
       <c r="O17" s="36">
         <f t="shared" si="6"/>
-        <v>179219.11</v>
+        <v>228634.11</v>
       </c>
       <c r="P17" s="37">
         <f t="shared" si="0"/>
-        <v>184596.11</v>
+        <v>235493.11</v>
       </c>
       <c r="Q17" s="18">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="R17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S17" s="16">
         <v>3420</v>
@@ -3969,24 +3983,24 @@
         <v>18</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" s="26"/>
       <c r="F18" s="29">
         <v>0.56999999999999995</v>
       </c>
       <c r="G18" s="30">
-        <v>9669.1200000000008</v>
-      </c>
-      <c r="H18" s="31">
+        <v>8857.1200000000008</v>
+      </c>
+      <c r="H18" s="188">
         <f>G18</f>
-        <v>9669.1200000000008</v>
+        <v>8857.1200000000008</v>
       </c>
       <c r="I18" s="32"/>
       <c r="J18" s="33">
@@ -3999,22 +4013,22 @@
       </c>
       <c r="L18" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>823.14269999999988</v>
       </c>
       <c r="M18" s="34">
         <f t="shared" si="5"/>
-        <v>8598.8972219999996</v>
+        <v>10146.672885</v>
       </c>
       <c r="N18" s="35">
         <v>0</v>
       </c>
       <c r="O18" s="36">
         <f t="shared" si="6"/>
-        <v>8599.1200000000008</v>
+        <v>10970.12</v>
       </c>
       <c r="P18" s="37">
         <f t="shared" si="0"/>
-        <v>8857.1200000000008</v>
+        <v>11299.12</v>
       </c>
       <c r="Q18" s="18">
         <f t="shared" si="7"/>
@@ -4036,28 +4050,29 @@
         <v>18</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19" s="26"/>
       <c r="F19" s="29">
         <v>0.52</v>
       </c>
       <c r="G19" s="30">
-        <v>8307.1299999999992</v>
-      </c>
-      <c r="H19" s="31">
-        <v>8556.1299999999992</v>
+        <v>7596.13</v>
+      </c>
+      <c r="H19" s="188">
+        <f>7824.13</f>
+        <v>7824.13</v>
       </c>
       <c r="I19" s="32"/>
       <c r="J19" s="33">
         <f t="shared" si="2"/>
-        <v>-249</v>
+        <v>-228</v>
       </c>
       <c r="K19" s="33">
         <f t="shared" si="3"/>
@@ -4065,22 +4080,22 @@
       </c>
       <c r="L19" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>750.93719999999996</v>
       </c>
       <c r="M19" s="34">
         <f t="shared" si="5"/>
-        <v>7844.6079919999993</v>
+        <v>9256.6138599999995</v>
       </c>
       <c r="N19" s="35">
         <v>0</v>
       </c>
       <c r="O19" s="36">
         <f t="shared" si="6"/>
-        <v>7596.13</v>
+        <v>9780.1299999999992</v>
       </c>
       <c r="P19" s="37">
         <f t="shared" si="0"/>
-        <v>7824.13</v>
+        <v>10073.129999999999</v>
       </c>
       <c r="Q19" s="18">
         <f t="shared" si="7"/>
@@ -4102,26 +4117,26 @@
         <v>19</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F20" s="29">
         <v>0.52</v>
       </c>
       <c r="G20" s="30">
-        <v>8564.14</v>
-      </c>
-      <c r="H20" s="31">
+        <v>7845.14</v>
+      </c>
+      <c r="H20" s="188">
         <f>G20</f>
-        <v>8564.14</v>
+        <v>7845.14</v>
       </c>
       <c r="I20" s="32"/>
       <c r="J20" s="33">
@@ -4134,22 +4149,22 @@
       </c>
       <c r="L20" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>750.93719999999996</v>
       </c>
       <c r="M20" s="34">
         <f t="shared" si="5"/>
-        <v>7844.6079919999993</v>
+        <v>9256.6138599999995</v>
       </c>
       <c r="N20" s="35">
         <v>0</v>
       </c>
       <c r="O20" s="36">
         <f t="shared" si="6"/>
-        <v>7845.14</v>
+        <v>10008.14</v>
       </c>
       <c r="P20" s="37">
         <f t="shared" si="0"/>
-        <v>8080.14</v>
+        <v>10308.14</v>
       </c>
       <c r="Q20" s="18">
         <f t="shared" si="7"/>
@@ -4171,24 +4186,24 @@
         <v>19</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E21" s="26"/>
       <c r="F21" s="29">
         <v>0.52</v>
       </c>
       <c r="G21" s="30">
-        <v>8564.15</v>
-      </c>
-      <c r="H21" s="31">
+        <v>7845.15</v>
+      </c>
+      <c r="H21" s="188">
         <f>G21</f>
-        <v>8564.15</v>
+        <v>7845.15</v>
       </c>
       <c r="I21" s="32"/>
       <c r="J21" s="33">
@@ -4201,22 +4216,22 @@
       </c>
       <c r="L21" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>750.93719999999996</v>
       </c>
       <c r="M21" s="34">
         <f t="shared" si="5"/>
-        <v>7844.6079919999993</v>
+        <v>9256.6138599999995</v>
       </c>
       <c r="N21" s="35">
         <v>0</v>
       </c>
       <c r="O21" s="36">
         <f t="shared" si="6"/>
-        <v>7845.15</v>
+        <v>10008.15</v>
       </c>
       <c r="P21" s="37">
         <f t="shared" si="0"/>
-        <v>8080.15</v>
+        <v>10308.15</v>
       </c>
       <c r="Q21" s="18">
         <f t="shared" si="7"/>
@@ -4238,24 +4253,24 @@
         <v>20</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E22" s="25"/>
       <c r="F22" s="29">
         <v>0.61</v>
       </c>
       <c r="G22" s="30">
-        <v>10046.16</v>
-      </c>
-      <c r="H22" s="31">
+        <v>9202.16</v>
+      </c>
+      <c r="H22" s="188">
         <f>G22</f>
-        <v>10046.16</v>
+        <v>9202.16</v>
       </c>
       <c r="I22" s="32"/>
       <c r="J22" s="33">
@@ -4268,22 +4283,22 @@
       </c>
       <c r="L22" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>880.9070999999999</v>
       </c>
       <c r="M22" s="34">
         <f t="shared" si="5"/>
-        <v>9202.3286059999991</v>
+        <v>10858.720105</v>
       </c>
       <c r="N22" s="35">
         <v>0</v>
       </c>
       <c r="O22" s="36">
         <f t="shared" si="6"/>
-        <v>9202.16</v>
+        <v>11740.16</v>
       </c>
       <c r="P22" s="37">
         <f t="shared" si="0"/>
-        <v>9478.16</v>
+        <v>12092.16</v>
       </c>
       <c r="Q22" s="18">
         <f t="shared" si="7"/>
@@ -4301,7 +4316,7 @@
       <c r="E23" s="25"/>
       <c r="F23" s="29"/>
       <c r="G23" s="38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H23" s="31" t="str">
         <f t="shared" ref="H23" si="8">G23</f>
@@ -4348,11 +4363,11 @@
       </c>
       <c r="G24" s="21">
         <f>SUM(G7:G23)</f>
-        <v>7041358.3599999994</v>
+        <v>7406319.3599999994</v>
       </c>
       <c r="H24" s="24">
         <f>SUM(H7:H23)</f>
-        <v>1393375.9</v>
+        <v>1248334.8199999998</v>
       </c>
       <c r="I24" s="24">
         <f>SUM(I7:I23)</f>
@@ -4362,23 +4377,23 @@
       <c r="K24" s="24"/>
       <c r="L24" s="24">
         <f>SUM(L7:L23)</f>
-        <v>0</v>
+        <v>144410.99999999997</v>
       </c>
       <c r="M24" s="24">
         <f>SUM(M7:M23)</f>
-        <v>1508578.4599999995</v>
+        <v>1780118.0499999998</v>
       </c>
       <c r="N24" s="24">
         <f>SUM(N7:N23)</f>
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="O24" s="47">
         <f>SUM(O7:O22)</f>
-        <v>7401010.3599999994</v>
+        <v>8317357.3599999994</v>
       </c>
       <c r="P24" s="47">
         <f>SUM(P7:P22)</f>
-        <v>7623038.3599999994</v>
+        <v>8566875.3599999994</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="12.75" customHeight="1">
@@ -4388,91 +4403,91 @@
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="15" customHeight="1">
-      <c r="D27" s="164" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" s="164"/>
-      <c r="F27" s="164"/>
-      <c r="G27" s="164"/>
-      <c r="H27" s="164"/>
-      <c r="I27" s="164"/>
-      <c r="J27" s="164"/>
-      <c r="K27" s="164"/>
-      <c r="L27" s="164"/>
-      <c r="M27" s="164"/>
-      <c r="N27" s="164"/>
-      <c r="O27" s="164"/>
+      <c r="D27" s="173" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="173"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="173"/>
+      <c r="H27" s="173"/>
+      <c r="I27" s="173"/>
+      <c r="J27" s="173"/>
+      <c r="K27" s="173"/>
+      <c r="L27" s="173"/>
+      <c r="M27" s="173"/>
+      <c r="N27" s="173"/>
+      <c r="O27" s="173"/>
       <c r="S27" s="16"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="164"/>
-      <c r="E28" s="164"/>
-      <c r="F28" s="164"/>
-      <c r="G28" s="164"/>
-      <c r="H28" s="164"/>
-      <c r="I28" s="164"/>
-      <c r="J28" s="164"/>
-      <c r="K28" s="164"/>
-      <c r="L28" s="164"/>
-      <c r="M28" s="164"/>
-      <c r="N28" s="164"/>
-      <c r="O28" s="164"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="173"/>
+      <c r="F28" s="173"/>
+      <c r="G28" s="173"/>
+      <c r="H28" s="173"/>
+      <c r="I28" s="173"/>
+      <c r="J28" s="173"/>
+      <c r="K28" s="173"/>
+      <c r="L28" s="173"/>
+      <c r="M28" s="173"/>
+      <c r="N28" s="173"/>
+      <c r="O28" s="173"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="164"/>
-      <c r="E29" s="164"/>
-      <c r="F29" s="164"/>
-      <c r="G29" s="164"/>
-      <c r="H29" s="164"/>
-      <c r="I29" s="164"/>
-      <c r="J29" s="164"/>
-      <c r="K29" s="164"/>
-      <c r="L29" s="164"/>
-      <c r="M29" s="164"/>
-      <c r="N29" s="164"/>
-      <c r="O29" s="164"/>
+      <c r="D29" s="173"/>
+      <c r="E29" s="173"/>
+      <c r="F29" s="173"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="173"/>
+      <c r="I29" s="173"/>
+      <c r="J29" s="173"/>
+      <c r="K29" s="173"/>
+      <c r="L29" s="173"/>
+      <c r="M29" s="173"/>
+      <c r="N29" s="173"/>
+      <c r="O29" s="173"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="164"/>
-      <c r="E30" s="164"/>
-      <c r="F30" s="164"/>
-      <c r="G30" s="164"/>
-      <c r="H30" s="164"/>
-      <c r="I30" s="164"/>
-      <c r="J30" s="164"/>
-      <c r="K30" s="164"/>
-      <c r="L30" s="164"/>
-      <c r="M30" s="164"/>
-      <c r="N30" s="164"/>
-      <c r="O30" s="164"/>
+      <c r="D30" s="173"/>
+      <c r="E30" s="173"/>
+      <c r="F30" s="173"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="173"/>
+      <c r="I30" s="173"/>
+      <c r="J30" s="173"/>
+      <c r="K30" s="173"/>
+      <c r="L30" s="173"/>
+      <c r="M30" s="173"/>
+      <c r="N30" s="173"/>
+      <c r="O30" s="173"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="164"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="164"/>
-      <c r="H31" s="164"/>
-      <c r="I31" s="164"/>
-      <c r="J31" s="164"/>
-      <c r="K31" s="164"/>
-      <c r="L31" s="164"/>
-      <c r="M31" s="164"/>
-      <c r="N31" s="164"/>
-      <c r="O31" s="164"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="173"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="173"/>
+      <c r="J31" s="173"/>
+      <c r="K31" s="173"/>
+      <c r="L31" s="173"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="173"/>
+      <c r="O31" s="173"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="164"/>
-      <c r="E32" s="164"/>
-      <c r="F32" s="164"/>
-      <c r="G32" s="164"/>
-      <c r="H32" s="164"/>
-      <c r="I32" s="164"/>
-      <c r="J32" s="164"/>
-      <c r="K32" s="164"/>
-      <c r="L32" s="164"/>
-      <c r="M32" s="164"/>
-      <c r="N32" s="164"/>
-      <c r="O32" s="164"/>
+      <c r="D32" s="173"/>
+      <c r="E32" s="173"/>
+      <c r="F32" s="173"/>
+      <c r="G32" s="173"/>
+      <c r="H32" s="173"/>
+      <c r="I32" s="173"/>
+      <c r="J32" s="173"/>
+      <c r="K32" s="173"/>
+      <c r="L32" s="173"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="173"/>
+      <c r="O32" s="173"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4507,7 +4522,7 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" s="141" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/2026/BELTRAN 34/Septiembre/Septiembre BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Septiembre/Septiembre BELTRAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BA7C1E-166B-449F-A16E-C581B61B006E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7370E4F1-32CC-4CDC-B1CD-63A192F7B3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="133">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -354,9 +354,6 @@
     <t>Carla Fabiana Silva</t>
   </si>
   <si>
-    <t>Matias Jose Medina Gonzalez</t>
-  </si>
-  <si>
     <t>Ivan Aguirre - Lucia daniela Toledo</t>
   </si>
   <si>
@@ -433,6 +430,9 @@
   </si>
   <si>
     <t>PREVISION EXTRAORDINARIA - Monto de inicio de demanda $144.411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belen </t>
   </si>
 </sst>
 </file>
@@ -448,7 +448,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -733,13 +733,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -1478,7 +1471,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1681,12 +1674,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1732,6 +1722,18 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1747,9 +1749,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1780,16 +1779,9 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="42" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -2257,41 +2249,41 @@
       <c r="D3" s="71"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A4" s="154" t="s">
+      <c r="A4" s="151" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="154"/>
+      <c r="B4" s="151"/>
       <c r="C4" s="72"/>
       <c r="D4" s="72"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="154"/>
-      <c r="B5" s="154"/>
+      <c r="A5" s="151"/>
+      <c r="B5" s="151"/>
       <c r="C5" s="72"/>
       <c r="D5" s="72"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="154"/>
-      <c r="B6" s="154"/>
+      <c r="A6" s="151"/>
+      <c r="B6" s="151"/>
       <c r="C6" s="72"/>
       <c r="D6" s="72"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="154"/>
-      <c r="B7" s="154"/>
+      <c r="A7" s="151"/>
+      <c r="B7" s="151"/>
       <c r="C7" s="72"/>
       <c r="D7" s="72"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="162" t="s">
-        <v>122</v>
+      <c r="B9" s="159" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="162"/>
+      <c r="B10" s="159"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="162"/>
+      <c r="B11" s="159"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="62"/>
@@ -2306,30 +2298,30 @@
       <c r="D13" s="62"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="154" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="157"/>
-      <c r="C14" s="157"/>
-      <c r="D14" s="157"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="157"/>
-      <c r="B15" s="157"/>
-      <c r="C15" s="157"/>
-      <c r="D15" s="157"/>
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="157"/>
-      <c r="B16" s="157"/>
-      <c r="C16" s="157"/>
-      <c r="D16" s="157"/>
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="157"/>
-      <c r="B17" s="157"/>
-      <c r="C17" s="157"/>
-      <c r="D17" s="157"/>
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
+      <c r="D17" s="154"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="A18" s="62"/>
@@ -2367,19 +2359,19 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A23" s="163" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" s="164"/>
-      <c r="C23" s="167">
+      <c r="A23" s="160" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="161"/>
+      <c r="C23" s="164">
         <v>0</v>
       </c>
       <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A24" s="165"/>
-      <c r="B24" s="166"/>
-      <c r="C24" s="168"/>
+      <c r="A24" s="162"/>
+      <c r="B24" s="163"/>
+      <c r="C24" s="165"/>
       <c r="D24" s="48"/>
     </row>
     <row r="25" spans="1:7">
@@ -2452,7 +2444,7 @@
     </row>
     <row r="33" spans="1:7" ht="22.5" customHeight="1">
       <c r="A33" s="97" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" s="113"/>
       <c r="C33" s="84">
@@ -2460,7 +2452,7 @@
       </c>
       <c r="D33" s="82"/>
       <c r="F33" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G33" s="4"/>
     </row>
@@ -2484,27 +2476,27 @@
       <c r="D35" s="27"/>
     </row>
     <row r="36" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A36" s="155" t="s">
-        <v>119</v>
-      </c>
-      <c r="B36" s="156"/>
-      <c r="C36" s="152">
+      <c r="A36" s="152" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" s="153"/>
+      <c r="C36" s="186">
         <v>89533</v>
       </c>
       <c r="D36" s="81" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="22.5" customHeight="1">
       <c r="A37" s="146" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B37" s="147"/>
-      <c r="C37" s="153">
+      <c r="C37" s="187">
         <v>5587.48</v>
       </c>
       <c r="D37" s="81" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" thickBot="1">
@@ -2591,11 +2583,11 @@
         <v>93</v>
       </c>
       <c r="B46" s="48"/>
-      <c r="C46" s="150">
+      <c r="C46" s="87">
         <v>66626.53</v>
       </c>
       <c r="D46" s="79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1">
@@ -2603,14 +2595,14 @@
         <v>94</v>
       </c>
       <c r="B47" s="48"/>
-      <c r="C47" s="150">
+      <c r="C47" s="87">
         <v>502776.73</v>
       </c>
       <c r="D47" s="79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" thickBot="1">
@@ -2633,39 +2625,39 @@
       <c r="D49" s="55"/>
     </row>
     <row r="50" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A50" s="155" t="s">
-        <v>109</v>
-      </c>
-      <c r="B50" s="156"/>
-      <c r="C50" s="150">
+      <c r="A50" s="152" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="153"/>
+      <c r="C50" s="87">
         <v>126000</v>
       </c>
       <c r="D50" s="79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="19.899999999999999" customHeight="1">
       <c r="A51" s="146" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="148"/>
+      <c r="C51" s="87">
+        <v>300000</v>
+      </c>
+      <c r="D51" s="77" t="s">
         <v>127</v>
       </c>
-      <c r="B51" s="148"/>
-      <c r="C51" s="150">
-        <v>300000</v>
-      </c>
-      <c r="D51" s="77" t="s">
-        <v>128</v>
-      </c>
     </row>
     <row r="52" spans="1:6" ht="41.25" customHeight="1">
-      <c r="A52" s="155" t="s">
+      <c r="A52" s="152" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="153"/>
+      <c r="C52" s="87">
+        <v>580730.54</v>
+      </c>
+      <c r="D52" s="77" t="s">
         <v>125</v>
-      </c>
-      <c r="B52" s="156"/>
-      <c r="C52" s="150">
-        <v>580730.54</v>
-      </c>
-      <c r="D52" s="77" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
@@ -2689,10 +2681,10 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B55" s="48"/>
-      <c r="C55" s="150">
+      <c r="C55" s="87">
         <v>69000</v>
       </c>
       <c r="D55" s="58"/>
@@ -2702,7 +2694,7 @@
         <v>101</v>
       </c>
       <c r="B56" s="48"/>
-      <c r="C56" s="150">
+      <c r="C56" s="87">
         <v>39863.769999999997</v>
       </c>
       <c r="D56" s="56"/>
@@ -2725,11 +2717,11 @@
       <c r="D58" s="60"/>
     </row>
     <row r="59" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A59" s="159" t="s">
-        <v>113</v>
-      </c>
-      <c r="B59" s="160"/>
-      <c r="C59" s="161"/>
+      <c r="A59" s="156" t="s">
+        <v>112</v>
+      </c>
+      <c r="B59" s="157"/>
+      <c r="C59" s="158"/>
       <c r="D59" s="61">
         <v>0</v>
       </c>
@@ -2804,7 +2796,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B69" s="128"/>
       <c r="C69" s="129"/>
@@ -2878,7 +2870,7 @@
       <c r="B77" s="62"/>
       <c r="C77" s="62"/>
       <c r="D77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2927,12 +2919,12 @@
       </c>
       <c r="C83" s="62"/>
       <c r="F83" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="39.75" customHeight="1">
-      <c r="A84" s="151" t="s">
-        <v>124</v>
+      <c r="A84" s="150" t="s">
+        <v>123</v>
       </c>
       <c r="B84" s="144">
         <v>-50000</v>
@@ -2975,14 +2967,14 @@
       <c r="D88" s="123"/>
     </row>
     <row r="89" spans="1:12">
-      <c r="A89" s="158" t="s">
+      <c r="A89" s="155" t="s">
         <v>45</v>
       </c>
-      <c r="B89" s="158"/>
+      <c r="B89" s="155"/>
     </row>
     <row r="90" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A90" s="158"/>
-      <c r="B90" s="158"/>
+      <c r="A90" s="155"/>
+      <c r="B90" s="155"/>
     </row>
     <row r="91" spans="1:12" ht="32.25" customHeight="1">
       <c r="A91" s="68"/>
@@ -3052,22 +3044,22 @@
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="99"/>
-      <c r="B1" s="169" t="str">
+      <c r="B1" s="170" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
       <c r="L1" s="100"/>
       <c r="M1" s="100"/>
       <c r="N1" s="100"/>
@@ -3076,16 +3068,16 @@
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
       <c r="A2" s="102"/>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
       <c r="L2" s="103"/>
       <c r="M2" s="103" t="s">
         <v>4</v>
@@ -3102,16 +3094,16 @@
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
       <c r="A3" s="105"/>
-      <c r="B3" s="171"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="171"/>
-      <c r="K3" s="171"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
       <c r="L3" s="106"/>
       <c r="M3" s="106" t="s">
         <v>55</v>
@@ -3143,31 +3135,31 @@
       <c r="P4" s="184"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="185" t="s">
+      <c r="A5" s="166" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="187" t="s">
+      <c r="B5" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="174" t="s">
+      <c r="C5" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="174" t="s">
+      <c r="D5" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="174" t="s">
+      <c r="E5" s="169" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="174" t="s">
+      <c r="F5" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="174" t="s">
+      <c r="G5" s="169" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="174" t="s">
+      <c r="H5" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="174" t="s">
+      <c r="I5" s="169" t="s">
         <v>42</v>
       </c>
       <c r="J5" s="178" t="s">
@@ -3188,21 +3180,21 @@
       <c r="O5" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="P5" s="172" t="s">
+      <c r="P5" s="173" t="s">
         <v>48</v>
       </c>
       <c r="S5" s="18"/>
       <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="186"/>
-      <c r="B6" s="187"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="174"/>
+      <c r="A6" s="167"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
       <c r="E6" s="175"/>
-      <c r="F6" s="174"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="174"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
+      <c r="H6" s="169"/>
       <c r="I6" s="175"/>
       <c r="J6" s="179"/>
       <c r="K6" s="177"/>
@@ -3213,7 +3205,7 @@
         <f>RESUMEN!B9</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="P6" s="172"/>
+      <c r="P6" s="173"/>
       <c r="S6" s="16">
         <v>65160</v>
       </c>
@@ -3308,7 +3300,7 @@
       <c r="G8" s="30">
         <v>173409.02</v>
       </c>
-      <c r="H8" s="188">
+      <c r="H8" s="31">
         <f>182266.14-H18</f>
         <v>173409.02000000002</v>
       </c>
@@ -3438,7 +3430,7 @@
         <v>84</v>
       </c>
       <c r="E10" s="78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F10" s="29">
         <v>7.37</v>
@@ -3446,7 +3438,7 @@
       <c r="G10" s="30">
         <v>159529.04</v>
       </c>
-      <c r="H10" s="188">
+      <c r="H10" s="31">
         <f>119027-H20</f>
         <v>111181.86</v>
       </c>
@@ -3507,7 +3499,7 @@
         <v>85</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F11" s="29">
         <v>10.68</v>
@@ -3515,7 +3507,7 @@
       <c r="G11" s="30">
         <v>161116.04999999999</v>
       </c>
-      <c r="H11" s="188">
+      <c r="H11" s="31">
         <f>G11</f>
         <v>161116.04999999999</v>
       </c>
@@ -3576,7 +3568,7 @@
         <v>86</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="F12" s="29">
         <v>6.95</v>
@@ -3584,7 +3576,7 @@
       <c r="G12" s="30">
         <v>104846.06</v>
       </c>
-      <c r="H12" s="188">
+      <c r="H12" s="31">
         <f>114048-H22</f>
         <v>104845.84</v>
       </c>
@@ -3653,7 +3645,7 @@
       <c r="G13" s="30">
         <v>103941.07</v>
       </c>
-      <c r="H13" s="188">
+      <c r="H13" s="31">
         <f>G13</f>
         <v>103941.07</v>
       </c>
@@ -3723,7 +3715,7 @@
       <c r="G14" s="30">
         <v>161116.07999999999</v>
       </c>
-      <c r="H14" s="188">
+      <c r="H14" s="31">
         <f>G14</f>
         <v>161116.07999999999</v>
       </c>
@@ -3784,7 +3776,7 @@
         <v>88</v>
       </c>
       <c r="E15" s="90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F15" s="91">
         <v>6.95</v>
@@ -3792,7 +3784,7 @@
       <c r="G15" s="31">
         <v>104846.09</v>
       </c>
-      <c r="H15" s="188">
+      <c r="H15" s="31">
         <v>107991.09</v>
       </c>
       <c r="I15" s="32"/>
@@ -3859,7 +3851,7 @@
       <c r="G16" s="30">
         <v>146479.1</v>
       </c>
-      <c r="H16" s="188">
+      <c r="H16" s="31">
         <v>103941</v>
       </c>
       <c r="I16" s="32"/>
@@ -3895,7 +3887,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S16" s="16">
         <v>71280</v>
@@ -3928,7 +3920,7 @@
       <c r="G17" s="30">
         <v>179219.11</v>
       </c>
-      <c r="H17" s="188">
+      <c r="H17" s="31">
         <f>G17</f>
         <v>179219.11</v>
       </c>
@@ -3965,7 +3957,7 @@
         <v>0.10999999999999999</v>
       </c>
       <c r="R17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S17" s="16">
         <v>3420</v>
@@ -3998,7 +3990,7 @@
       <c r="G18" s="30">
         <v>8857.1200000000008</v>
       </c>
-      <c r="H18" s="188">
+      <c r="H18" s="31">
         <f>G18</f>
         <v>8857.1200000000008</v>
       </c>
@@ -4065,7 +4057,7 @@
       <c r="G19" s="30">
         <v>7596.13</v>
       </c>
-      <c r="H19" s="188">
+      <c r="H19" s="31">
         <f>7824.13</f>
         <v>7824.13</v>
       </c>
@@ -4134,7 +4126,7 @@
       <c r="G20" s="30">
         <v>7845.14</v>
       </c>
-      <c r="H20" s="188">
+      <c r="H20" s="31">
         <f>G20</f>
         <v>7845.14</v>
       </c>
@@ -4201,7 +4193,7 @@
       <c r="G21" s="30">
         <v>7845.15</v>
       </c>
-      <c r="H21" s="188">
+      <c r="H21" s="31">
         <f>G21</f>
         <v>7845.15</v>
       </c>
@@ -4261,14 +4253,16 @@
       <c r="D22" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="25"/>
+      <c r="E22" s="25" t="s">
+        <v>132</v>
+      </c>
       <c r="F22" s="29">
         <v>0.61</v>
       </c>
       <c r="G22" s="30">
         <v>9202.16</v>
       </c>
-      <c r="H22" s="188">
+      <c r="H22" s="31">
         <f>G22</f>
         <v>9202.16</v>
       </c>
@@ -4365,7 +4359,7 @@
         <f>SUM(G7:G23)</f>
         <v>7406319.3599999994</v>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="185">
         <f>SUM(H7:H23)</f>
         <v>1248334.8199999998</v>
       </c>
@@ -4403,99 +4397,94 @@
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="15" customHeight="1">
-      <c r="D27" s="173" t="s">
+      <c r="D27" s="174" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="173"/>
-      <c r="F27" s="173"/>
-      <c r="G27" s="173"/>
-      <c r="H27" s="173"/>
-      <c r="I27" s="173"/>
-      <c r="J27" s="173"/>
-      <c r="K27" s="173"/>
-      <c r="L27" s="173"/>
-      <c r="M27" s="173"/>
-      <c r="N27" s="173"/>
-      <c r="O27" s="173"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="174"/>
+      <c r="G27" s="174"/>
+      <c r="H27" s="174"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="174"/>
+      <c r="L27" s="174"/>
+      <c r="M27" s="174"/>
+      <c r="N27" s="174"/>
+      <c r="O27" s="174"/>
       <c r="S27" s="16"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="173"/>
-      <c r="E28" s="173"/>
-      <c r="F28" s="173"/>
-      <c r="G28" s="173"/>
-      <c r="H28" s="173"/>
-      <c r="I28" s="173"/>
-      <c r="J28" s="173"/>
-      <c r="K28" s="173"/>
-      <c r="L28" s="173"/>
-      <c r="M28" s="173"/>
-      <c r="N28" s="173"/>
-      <c r="O28" s="173"/>
+      <c r="D28" s="174"/>
+      <c r="E28" s="174"/>
+      <c r="F28" s="174"/>
+      <c r="G28" s="174"/>
+      <c r="H28" s="174"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="174"/>
+      <c r="L28" s="174"/>
+      <c r="M28" s="174"/>
+      <c r="N28" s="174"/>
+      <c r="O28" s="174"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="173"/>
-      <c r="E29" s="173"/>
-      <c r="F29" s="173"/>
-      <c r="G29" s="173"/>
-      <c r="H29" s="173"/>
-      <c r="I29" s="173"/>
-      <c r="J29" s="173"/>
-      <c r="K29" s="173"/>
-      <c r="L29" s="173"/>
-      <c r="M29" s="173"/>
-      <c r="N29" s="173"/>
-      <c r="O29" s="173"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="174"/>
+      <c r="F29" s="174"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="174"/>
+      <c r="I29" s="174"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="174"/>
+      <c r="L29" s="174"/>
+      <c r="M29" s="174"/>
+      <c r="N29" s="174"/>
+      <c r="O29" s="174"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="173"/>
-      <c r="E30" s="173"/>
-      <c r="F30" s="173"/>
-      <c r="G30" s="173"/>
-      <c r="H30" s="173"/>
-      <c r="I30" s="173"/>
-      <c r="J30" s="173"/>
-      <c r="K30" s="173"/>
-      <c r="L30" s="173"/>
-      <c r="M30" s="173"/>
-      <c r="N30" s="173"/>
-      <c r="O30" s="173"/>
+      <c r="D30" s="174"/>
+      <c r="E30" s="174"/>
+      <c r="F30" s="174"/>
+      <c r="G30" s="174"/>
+      <c r="H30" s="174"/>
+      <c r="I30" s="174"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="174"/>
+      <c r="L30" s="174"/>
+      <c r="M30" s="174"/>
+      <c r="N30" s="174"/>
+      <c r="O30" s="174"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="173"/>
-      <c r="E31" s="173"/>
-      <c r="F31" s="173"/>
-      <c r="G31" s="173"/>
-      <c r="H31" s="173"/>
-      <c r="I31" s="173"/>
-      <c r="J31" s="173"/>
-      <c r="K31" s="173"/>
-      <c r="L31" s="173"/>
-      <c r="M31" s="173"/>
-      <c r="N31" s="173"/>
-      <c r="O31" s="173"/>
+      <c r="D31" s="174"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="174"/>
+      <c r="G31" s="174"/>
+      <c r="H31" s="174"/>
+      <c r="I31" s="174"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="174"/>
+      <c r="L31" s="174"/>
+      <c r="M31" s="174"/>
+      <c r="N31" s="174"/>
+      <c r="O31" s="174"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="173"/>
-      <c r="E32" s="173"/>
-      <c r="F32" s="173"/>
-      <c r="G32" s="173"/>
-      <c r="H32" s="173"/>
-      <c r="I32" s="173"/>
-      <c r="J32" s="173"/>
-      <c r="K32" s="173"/>
-      <c r="L32" s="173"/>
-      <c r="M32" s="173"/>
-      <c r="N32" s="173"/>
-      <c r="O32" s="173"/>
+      <c r="D32" s="174"/>
+      <c r="E32" s="174"/>
+      <c r="F32" s="174"/>
+      <c r="G32" s="174"/>
+      <c r="H32" s="174"/>
+      <c r="I32" s="174"/>
+      <c r="J32" s="174"/>
+      <c r="K32" s="174"/>
+      <c r="L32" s="174"/>
+      <c r="M32" s="174"/>
+      <c r="N32" s="174"/>
+      <c r="O32" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D27:O32"/>
@@ -4509,6 +4498,11 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
@@ -4522,7 +4516,7 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" s="141" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/2026/BELTRAN 34/Septiembre/Septiembre BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Septiembre/Septiembre BELTRAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7370E4F1-32CC-4CDC-B1CD-63A192F7B3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81F7557-4D58-443D-881A-EFC49E29A873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -396,9 +396,6 @@
     <t>Seguro - Sra. Soledad - La Holando - Poliza nro. 690173-2</t>
   </si>
   <si>
-    <t>Hay una diferencia de caja correspondiente a un gasto de AYSA a solucionar en S3ptiembr3</t>
-  </si>
-  <si>
     <t>VTO 16/10</t>
   </si>
   <si>
@@ -433,6 +430,9 @@
   </si>
   <si>
     <t xml:space="preserve">Belen </t>
+  </si>
+  <si>
+    <t>Hay una diferencia de caja correspondiente a un gasto de AYSA a solucionar en octubr3</t>
   </si>
 </sst>
 </file>
@@ -1677,111 +1677,111 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -2249,41 +2249,41 @@
       <c r="D3" s="71"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A4" s="151" t="s">
+      <c r="A4" s="154" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="151"/>
+      <c r="B4" s="154"/>
       <c r="C4" s="72"/>
       <c r="D4" s="72"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="151"/>
-      <c r="B5" s="151"/>
+      <c r="A5" s="154"/>
+      <c r="B5" s="154"/>
       <c r="C5" s="72"/>
       <c r="D5" s="72"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="151"/>
-      <c r="B6" s="151"/>
+      <c r="A6" s="154"/>
+      <c r="B6" s="154"/>
       <c r="C6" s="72"/>
       <c r="D6" s="72"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="151"/>
+      <c r="A7" s="154"/>
+      <c r="B7" s="154"/>
       <c r="C7" s="72"/>
       <c r="D7" s="72"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="159" t="s">
-        <v>121</v>
+      <c r="B9" s="162" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="159"/>
+      <c r="B10" s="162"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="159"/>
+      <c r="B11" s="162"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="62"/>
@@ -2298,30 +2298,30 @@
       <c r="D13" s="62"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="154" t="s">
+      <c r="A14" s="157" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="154"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
+      <c r="B14" s="157"/>
+      <c r="C14" s="157"/>
+      <c r="D14" s="157"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="154"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
+      <c r="A15" s="157"/>
+      <c r="B15" s="157"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="157"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="154"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
+      <c r="A16" s="157"/>
+      <c r="B16" s="157"/>
+      <c r="C16" s="157"/>
+      <c r="D16" s="157"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="154"/>
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
+      <c r="A17" s="157"/>
+      <c r="B17" s="157"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="157"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="A18" s="62"/>
@@ -2359,19 +2359,19 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A23" s="160" t="s">
-        <v>130</v>
-      </c>
-      <c r="B23" s="161"/>
-      <c r="C23" s="164">
+      <c r="A23" s="163" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="164"/>
+      <c r="C23" s="167">
         <v>0</v>
       </c>
       <c r="D23" s="48"/>
     </row>
     <row r="24" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A24" s="162"/>
-      <c r="B24" s="163"/>
-      <c r="C24" s="165"/>
+      <c r="A24" s="165"/>
+      <c r="B24" s="166"/>
+      <c r="C24" s="168"/>
       <c r="D24" s="48"/>
     </row>
     <row r="25" spans="1:7">
@@ -2444,7 +2444,7 @@
     </row>
     <row r="33" spans="1:7" ht="22.5" customHeight="1">
       <c r="A33" s="97" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="113"/>
       <c r="C33" s="84">
@@ -2476,15 +2476,15 @@
       <c r="D35" s="27"/>
     </row>
     <row r="36" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A36" s="152" t="s">
+      <c r="A36" s="155" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="153"/>
-      <c r="C36" s="186">
+      <c r="B36" s="156"/>
+      <c r="C36" s="152">
         <v>89533</v>
       </c>
       <c r="D36" s="81" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="22.5" customHeight="1">
@@ -2492,11 +2492,11 @@
         <v>119</v>
       </c>
       <c r="B37" s="147"/>
-      <c r="C37" s="187">
+      <c r="C37" s="153">
         <v>5587.48</v>
       </c>
       <c r="D37" s="81" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" thickBot="1">
@@ -2587,7 +2587,7 @@
         <v>66626.53</v>
       </c>
       <c r="D46" s="79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1">
@@ -2599,7 +2599,7 @@
         <v>502776.73</v>
       </c>
       <c r="D47" s="79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F47" t="s">
         <v>114</v>
@@ -2625,39 +2625,39 @@
       <c r="D49" s="55"/>
     </row>
     <row r="50" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="155" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="153"/>
+      <c r="B50" s="156"/>
       <c r="C50" s="87">
         <v>126000</v>
       </c>
       <c r="D50" s="79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="19.899999999999999" customHeight="1">
       <c r="A51" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B51" s="148"/>
       <c r="C51" s="87">
         <v>300000</v>
       </c>
       <c r="D51" s="77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="41.25" customHeight="1">
-      <c r="A52" s="152" t="s">
-        <v>124</v>
-      </c>
-      <c r="B52" s="153"/>
+      <c r="A52" s="155" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="156"/>
       <c r="C52" s="87">
         <v>580730.54</v>
       </c>
       <c r="D52" s="77" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
@@ -2717,11 +2717,11 @@
       <c r="D58" s="60"/>
     </row>
     <row r="59" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A59" s="156" t="s">
+      <c r="A59" s="159" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="157"/>
-      <c r="C59" s="158"/>
+      <c r="B59" s="160"/>
+      <c r="C59" s="161"/>
       <c r="D59" s="61">
         <v>0</v>
       </c>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="128" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B69" s="128"/>
       <c r="C69" s="129"/>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="C83" s="62"/>
       <c r="F83" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="39.75" customHeight="1">
       <c r="A84" s="150" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B84" s="144">
         <v>-50000</v>
@@ -2967,14 +2967,14 @@
       <c r="D88" s="123"/>
     </row>
     <row r="89" spans="1:12">
-      <c r="A89" s="155" t="s">
+      <c r="A89" s="158" t="s">
         <v>45</v>
       </c>
-      <c r="B89" s="155"/>
+      <c r="B89" s="158"/>
     </row>
     <row r="90" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A90" s="155"/>
-      <c r="B90" s="155"/>
+      <c r="A90" s="158"/>
+      <c r="B90" s="158"/>
     </row>
     <row r="91" spans="1:12" ht="32.25" customHeight="1">
       <c r="A91" s="68"/>
@@ -3044,22 +3044,22 @@
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="99"/>
-      <c r="B1" s="170" t="str">
+      <c r="B1" s="169" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
       <c r="L1" s="100"/>
       <c r="M1" s="100"/>
       <c r="N1" s="100"/>
@@ -3068,16 +3068,16 @@
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
       <c r="A2" s="102"/>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="170"/>
       <c r="L2" s="103"/>
       <c r="M2" s="103" t="s">
         <v>4</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
       <c r="A3" s="105"/>
-      <c r="B3" s="172"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
       <c r="L3" s="106"/>
       <c r="M3" s="106" t="s">
         <v>55</v>
@@ -3135,31 +3135,31 @@
       <c r="P4" s="184"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="166" t="s">
+      <c r="A5" s="185" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="168" t="s">
+      <c r="B5" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="169" t="s">
+      <c r="C5" s="174" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="169" t="s">
+      <c r="D5" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="169" t="s">
+      <c r="E5" s="174" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="169" t="s">
+      <c r="F5" s="174" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="169" t="s">
+      <c r="G5" s="174" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="169" t="s">
+      <c r="H5" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="169" t="s">
+      <c r="I5" s="174" t="s">
         <v>42</v>
       </c>
       <c r="J5" s="178" t="s">
@@ -3180,21 +3180,21 @@
       <c r="O5" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="P5" s="173" t="s">
+      <c r="P5" s="172" t="s">
         <v>48</v>
       </c>
       <c r="S5" s="18"/>
       <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="167"/>
-      <c r="B6" s="168"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="169"/>
+      <c r="A6" s="186"/>
+      <c r="B6" s="187"/>
+      <c r="C6" s="174"/>
+      <c r="D6" s="174"/>
       <c r="E6" s="175"/>
-      <c r="F6" s="169"/>
-      <c r="G6" s="169"/>
-      <c r="H6" s="169"/>
+      <c r="F6" s="174"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="174"/>
       <c r="I6" s="175"/>
       <c r="J6" s="179"/>
       <c r="K6" s="177"/>
@@ -3205,7 +3205,7 @@
         <f>RESUMEN!B9</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="P6" s="173"/>
+      <c r="P6" s="172"/>
       <c r="S6" s="16">
         <v>65160</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>86</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F12" s="29">
         <v>6.95</v>
@@ -4254,7 +4254,7 @@
         <v>86</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F22" s="29">
         <v>0.61</v>
@@ -4359,7 +4359,7 @@
         <f>SUM(G7:G23)</f>
         <v>7406319.3599999994</v>
       </c>
-      <c r="H24" s="185">
+      <c r="H24" s="151">
         <f>SUM(H7:H23)</f>
         <v>1248334.8199999998</v>
       </c>
@@ -4397,94 +4397,99 @@
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="15" customHeight="1">
-      <c r="D27" s="174" t="s">
+      <c r="D27" s="173" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="174"/>
-      <c r="F27" s="174"/>
-      <c r="G27" s="174"/>
-      <c r="H27" s="174"/>
-      <c r="I27" s="174"/>
-      <c r="J27" s="174"/>
-      <c r="K27" s="174"/>
-      <c r="L27" s="174"/>
-      <c r="M27" s="174"/>
-      <c r="N27" s="174"/>
-      <c r="O27" s="174"/>
+      <c r="E27" s="173"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="173"/>
+      <c r="H27" s="173"/>
+      <c r="I27" s="173"/>
+      <c r="J27" s="173"/>
+      <c r="K27" s="173"/>
+      <c r="L27" s="173"/>
+      <c r="M27" s="173"/>
+      <c r="N27" s="173"/>
+      <c r="O27" s="173"/>
       <c r="S27" s="16"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="174"/>
-      <c r="E28" s="174"/>
-      <c r="F28" s="174"/>
-      <c r="G28" s="174"/>
-      <c r="H28" s="174"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="174"/>
-      <c r="K28" s="174"/>
-      <c r="L28" s="174"/>
-      <c r="M28" s="174"/>
-      <c r="N28" s="174"/>
-      <c r="O28" s="174"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="173"/>
+      <c r="F28" s="173"/>
+      <c r="G28" s="173"/>
+      <c r="H28" s="173"/>
+      <c r="I28" s="173"/>
+      <c r="J28" s="173"/>
+      <c r="K28" s="173"/>
+      <c r="L28" s="173"/>
+      <c r="M28" s="173"/>
+      <c r="N28" s="173"/>
+      <c r="O28" s="173"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="174"/>
-      <c r="E29" s="174"/>
-      <c r="F29" s="174"/>
-      <c r="G29" s="174"/>
-      <c r="H29" s="174"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="174"/>
-      <c r="K29" s="174"/>
-      <c r="L29" s="174"/>
-      <c r="M29" s="174"/>
-      <c r="N29" s="174"/>
-      <c r="O29" s="174"/>
+      <c r="D29" s="173"/>
+      <c r="E29" s="173"/>
+      <c r="F29" s="173"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="173"/>
+      <c r="I29" s="173"/>
+      <c r="J29" s="173"/>
+      <c r="K29" s="173"/>
+      <c r="L29" s="173"/>
+      <c r="M29" s="173"/>
+      <c r="N29" s="173"/>
+      <c r="O29" s="173"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="174"/>
-      <c r="E30" s="174"/>
-      <c r="F30" s="174"/>
-      <c r="G30" s="174"/>
-      <c r="H30" s="174"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="174"/>
-      <c r="K30" s="174"/>
-      <c r="L30" s="174"/>
-      <c r="M30" s="174"/>
-      <c r="N30" s="174"/>
-      <c r="O30" s="174"/>
+      <c r="D30" s="173"/>
+      <c r="E30" s="173"/>
+      <c r="F30" s="173"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="173"/>
+      <c r="I30" s="173"/>
+      <c r="J30" s="173"/>
+      <c r="K30" s="173"/>
+      <c r="L30" s="173"/>
+      <c r="M30" s="173"/>
+      <c r="N30" s="173"/>
+      <c r="O30" s="173"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="174"/>
-      <c r="E31" s="174"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="174"/>
-      <c r="H31" s="174"/>
-      <c r="I31" s="174"/>
-      <c r="J31" s="174"/>
-      <c r="K31" s="174"/>
-      <c r="L31" s="174"/>
-      <c r="M31" s="174"/>
-      <c r="N31" s="174"/>
-      <c r="O31" s="174"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="173"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="173"/>
+      <c r="J31" s="173"/>
+      <c r="K31" s="173"/>
+      <c r="L31" s="173"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="173"/>
+      <c r="O31" s="173"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="174"/>
-      <c r="E32" s="174"/>
-      <c r="F32" s="174"/>
-      <c r="G32" s="174"/>
-      <c r="H32" s="174"/>
-      <c r="I32" s="174"/>
-      <c r="J32" s="174"/>
-      <c r="K32" s="174"/>
-      <c r="L32" s="174"/>
-      <c r="M32" s="174"/>
-      <c r="N32" s="174"/>
-      <c r="O32" s="174"/>
+      <c r="D32" s="173"/>
+      <c r="E32" s="173"/>
+      <c r="F32" s="173"/>
+      <c r="G32" s="173"/>
+      <c r="H32" s="173"/>
+      <c r="I32" s="173"/>
+      <c r="J32" s="173"/>
+      <c r="K32" s="173"/>
+      <c r="L32" s="173"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="173"/>
+      <c r="O32" s="173"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D27:O32"/>
@@ -4498,11 +4503,6 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
